--- a/artfynd/A 23219-2024 artfynd.xlsx
+++ b/artfynd/A 23219-2024 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>117961177</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>117960760</v>
       </c>
       <c r="B5" t="n">
-        <v>104929</v>
+        <v>104931</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
